--- a/SQExcel.Portal/src/content/docs/ja/docs/images/start-page/start-page.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/start-page/start-page.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\start-page\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\start-page\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C05FDDA-9DC5-4AA0-8723-970A7BBFFC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D39F34C-16F4-4B48-A275-C05EEDCCE561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2330" yWindow="1970" windowWidth="16830" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3072" yWindow="3072" windowWidth="16680" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="START-PAGE" sheetId="3" r:id="rId1"/>
@@ -988,22 +988,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>216646</xdr:colOff>
+      <xdr:colOff>174171</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>29883</xdr:rowOff>
+      <xdr:rowOff>54430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>213658</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>133074</xdr:rowOff>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>115771</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>44049</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="9" name="グループ化 8">
+        <xdr:cNvPr id="20" name="グループ化 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47681354-090B-04DB-A6E9-8819CC5FECB0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4852A49A-4FF2-35C9-A7B9-C4AD2A9AA8BD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1011,18 +1011,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="452503" y="937026"/>
-          <a:ext cx="10846441" cy="7133548"/>
-          <a:chOff x="451596" y="944283"/>
-          <a:chExt cx="10804712" cy="7189791"/>
+          <a:off x="413657" y="968830"/>
+          <a:ext cx="10000000" cy="6847619"/>
+          <a:chOff x="410391" y="968830"/>
+          <a:chExt cx="9862840" cy="6847619"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="2" name="図 1">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F056085-106E-5226-593F-F7208E9CC6D2}"/>
+          <xdr:cNvPr id="16" name="図 15">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DB77A38-5DA3-B616-5732-6B94A056ABB7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1038,8 +1038,8 @@
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="451596" y="944283"/>
-            <a:ext cx="10804712" cy="7189791"/>
+            <a:off x="410391" y="968830"/>
+            <a:ext cx="9862840" cy="6847619"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1059,8 +1059,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="515258" y="1507750"/>
-            <a:ext cx="6470649" cy="3118679"/>
+            <a:off x="514492" y="1507750"/>
+            <a:ext cx="5812285" cy="3118679"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1114,8 +1114,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3177535" y="1453243"/>
-            <a:ext cx="462380" cy="271067"/>
+            <a:off x="3192256" y="1453243"/>
+            <a:ext cx="464777" cy="271067"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
@@ -1174,8 +1174,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="10301435" y="2028370"/>
-            <a:ext cx="462381" cy="272882"/>
+            <a:off x="9302014" y="2028370"/>
+            <a:ext cx="464779" cy="272882"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
@@ -1234,8 +1234,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="10301435" y="3363686"/>
-            <a:ext cx="469477" cy="271067"/>
+            <a:off x="9302014" y="3276600"/>
+            <a:ext cx="472012" cy="271067"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
@@ -1294,8 +1294,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="10301435" y="4542971"/>
-            <a:ext cx="469477" cy="272882"/>
+            <a:off x="9302014" y="4434113"/>
+            <a:ext cx="472012" cy="272882"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
@@ -1354,8 +1354,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="9560298" y="5769429"/>
-            <a:ext cx="469477" cy="271067"/>
+            <a:off x="8708761" y="5573486"/>
+            <a:ext cx="472012" cy="271067"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
@@ -1450,155 +1450,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>9072</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>27215</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>191952</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>82890</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F43A4217-09CB-A4B0-16B9-246534AF8208}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="480786" y="13407572"/>
-          <a:ext cx="8673737" cy="5271747"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>119743</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>154060</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="図 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B387CFC-8A4F-578B-BBBF-171E62830B57}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="469900" y="19659601"/>
-          <a:ext cx="10801350" cy="8155059"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>157</xdr:row>
-      <xdr:rowOff>158044</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78FE3AFB-8EDC-CD9F-CF93-BC8FECC53B5F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="469900" y="28575001"/>
-          <a:ext cx="10801350" cy="7473243"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>161</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>184</xdr:row>
-      <xdr:rowOff>195375</xdr:rowOff>
+      <xdr:colOff>51707</xdr:colOff>
+      <xdr:row>183</xdr:row>
+      <xdr:rowOff>182195</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="18" name="グループ化 17">
+        <xdr:cNvPr id="28" name="グループ化 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{577E235C-628F-77AE-ACA4-D698032EBC2F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26E39036-E3D6-5D7C-654B-96A1AAFDF66F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1606,18 +1474,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="471714" y="36512500"/>
-          <a:ext cx="10842172" cy="5411446"/>
-          <a:chOff x="469900" y="36804600"/>
-          <a:chExt cx="10801350" cy="5453175"/>
+          <a:off x="359229" y="36401828"/>
+          <a:ext cx="10948307" cy="5614167"/>
+          <a:chOff x="355963" y="36401828"/>
+          <a:chExt cx="10798084" cy="5614167"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="15" name="図 14">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58BE5B9E-5F71-FF81-236F-E6CFAEDC3C0D}"/>
+          <xdr:cNvPr id="27" name="図 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83F1184C-2D0C-B916-CF5D-0819F0AFE7B6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1626,15 +1494,15 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="469900" y="36804600"/>
-            <a:ext cx="10801350" cy="5453175"/>
+            <a:off x="355963" y="36401828"/>
+            <a:ext cx="10798084" cy="5614167"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1654,13 +1522,13 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="8431891" y="39985043"/>
-            <a:ext cx="2430236" cy="513443"/>
+            <a:off x="7648713" y="39680245"/>
+            <a:ext cx="2541404" cy="488042"/>
           </a:xfrm>
           <a:prstGeom prst="wedgeRectCallout">
             <a:avLst>
-              <a:gd name="adj1" fmla="val -10177"/>
-              <a:gd name="adj2" fmla="val -105511"/>
+              <a:gd name="adj1" fmla="val -7979"/>
+              <a:gd name="adj2" fmla="val -186076"/>
             </a:avLst>
           </a:prstGeom>
           <a:ln w="19050">
@@ -1710,7 +1578,7 @@
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>ファイルをダブルクリックす。</a:t>
+              <a:t>ファイルをダブルクリックする。</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
@@ -1721,22 +1589,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>36286</xdr:colOff>
-      <xdr:row>188</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:colOff>32658</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>32657</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>29029</xdr:colOff>
-      <xdr:row>223</xdr:row>
-      <xdr:rowOff>217560</xdr:rowOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>169818</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>116663</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="図 18">
+        <xdr:cNvPr id="21" name="図 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADD9FB6F-0B2C-C311-EB2A-F835211C13E9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E89FB51-D082-4CA7-6094-509D0B381F04}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1745,15 +1613,196 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="508000" y="42699214"/>
-          <a:ext cx="10842172" cy="8091560"/>
+          <a:off x="511629" y="13520057"/>
+          <a:ext cx="8758646" cy="5341806"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>217714</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>134374</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="図 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB40D38D-F7B1-3BA2-69FA-E1266C0F1713}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="478972" y="19648714"/>
+          <a:ext cx="10948307" cy="7689060"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>158044</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="24" name="グループ化 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40DD2E4A-862C-7011-AFC1-4053C0661C60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="478971" y="28117801"/>
+          <a:ext cx="11005458" cy="7473243"/>
+          <a:chOff x="472440" y="28117801"/>
+          <a:chExt cx="10858500" cy="7473243"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="14" name="図 13">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78FE3AFB-8EDC-CD9F-CF93-BC8FECC53B5F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="472440" y="28117801"/>
+            <a:ext cx="10858500" cy="7473243"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="23" name="図 22">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14F00650-62ED-49A0-8020-FDC4F9B34DE6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="603069" y="28204886"/>
+            <a:ext cx="206313" cy="219106"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>186</xdr:row>
+      <xdr:rowOff>21771</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>8163</xdr:colOff>
+      <xdr:row>219</xdr:row>
+      <xdr:rowOff>167031</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="図 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EED1873-885E-4ABA-019F-E7ACC83A6364}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="315685" y="42541371"/>
+          <a:ext cx="10948307" cy="7689060"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1793,8 +1842,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="691776" y="743448"/>
-          <a:ext cx="6056033" cy="5032687"/>
+          <a:off x="694765" y="747930"/>
+          <a:ext cx="6096373" cy="5064063"/>
           <a:chOff x="698500" y="436033"/>
           <a:chExt cx="6146800" cy="4969934"/>
         </a:xfrm>
@@ -3995,8 +4044,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="254000" y="7933766"/>
-          <a:ext cx="8520057" cy="6579719"/>
+          <a:off x="255494" y="7984566"/>
+          <a:ext cx="8573845" cy="6621554"/>
           <a:chOff x="234950" y="6400801"/>
           <a:chExt cx="8641080" cy="6496049"/>
         </a:xfrm>
@@ -4259,8 +4308,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="15583649"/>
-          <a:ext cx="8520057" cy="5343485"/>
+          <a:off x="233082" y="15683755"/>
+          <a:ext cx="8573845" cy="5377850"/>
           <a:chOff x="234950" y="14240437"/>
           <a:chExt cx="8641080" cy="5274756"/>
         </a:xfrm>
@@ -4699,8 +4748,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="67464747"/>
-          <a:ext cx="10650071" cy="8259649"/>
+          <a:off x="233082" y="67899536"/>
+          <a:ext cx="10717306" cy="8311942"/>
           <a:chOff x="217714" y="64949614"/>
           <a:chExt cx="10800443" cy="8155060"/>
         </a:xfrm>
@@ -4864,8 +4913,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="58396522"/>
-          <a:ext cx="10650071" cy="7946338"/>
+          <a:off x="233082" y="58773040"/>
+          <a:ext cx="10717306" cy="7997138"/>
           <a:chOff x="234950" y="56500487"/>
           <a:chExt cx="10801350" cy="7844738"/>
         </a:xfrm>
@@ -5142,8 +5191,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="240658" y="77219466"/>
-          <a:ext cx="10645802" cy="6857194"/>
+          <a:off x="242152" y="77717008"/>
+          <a:ext cx="10714532" cy="6902017"/>
           <a:chOff x="226785" y="75309984"/>
           <a:chExt cx="10800443" cy="6767548"/>
         </a:xfrm>
@@ -5473,8 +5522,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9039410" y="1579284"/>
-          <a:ext cx="6060968" cy="3673815"/>
+          <a:off x="9097681" y="1588249"/>
+          <a:ext cx="6099815" cy="3697721"/>
           <a:chOff x="9170519" y="1561355"/>
           <a:chExt cx="6148374" cy="3626328"/>
         </a:xfrm>
@@ -6904,8 +6953,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="18534529" y="1875117"/>
-          <a:ext cx="4176059" cy="5353423"/>
+          <a:off x="18654058" y="1887070"/>
+          <a:ext cx="4202954" cy="5387788"/>
           <a:chOff x="18810940" y="1513541"/>
           <a:chExt cx="4236571" cy="5284693"/>
         </a:xfrm>
@@ -8208,8 +8257,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="249731" y="89474701"/>
-          <a:ext cx="10645802" cy="6853188"/>
+          <a:off x="251225" y="90051430"/>
+          <a:ext cx="10714532" cy="6896517"/>
           <a:chOff x="253093" y="88321242"/>
           <a:chExt cx="10800443" cy="6766529"/>
         </a:xfrm>
@@ -8327,8 +8376,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="249731" y="97571218"/>
-          <a:ext cx="10645802" cy="6853190"/>
+          <a:off x="251225" y="98200242"/>
+          <a:ext cx="10714532" cy="6896519"/>
           <a:chOff x="253093" y="96313171"/>
           <a:chExt cx="10800443" cy="6766531"/>
         </a:xfrm>
@@ -8686,13 +8735,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247D8D20-CE8B-4D82-A6C6-EA8B8BD03E4C}">
-  <dimension ref="A2:CD573"/>
-  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A2:CD571"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="3.08203125" style="1"/>
+    <col min="1" max="16384" width="3.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:82" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:82" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -8700,17 +8749,17 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:82" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:82" x14ac:dyDescent="0.45">
       <c r="B3" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AN3" s="2"/>
       <c r="CD3" s="2"/>
     </row>
-    <row r="33" spans="1:82" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:82" x14ac:dyDescent="0.45">
       <c r="B33" s="2"/>
     </row>
-    <row r="38" spans="1:82" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:82" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
@@ -8718,17 +8767,17 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:82" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:82" x14ac:dyDescent="0.45">
       <c r="B39" s="2" t="s">
         <v>49</v>
       </c>
       <c r="AN39" s="2"/>
       <c r="CD39" s="2"/>
     </row>
-    <row r="42" spans="1:82" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:82" x14ac:dyDescent="0.45">
       <c r="B42" s="2"/>
     </row>
-    <row r="58" spans="1:82" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:82" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
         <v>0</v>
       </c>
@@ -8736,20 +8785,20 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:82" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:82" x14ac:dyDescent="0.45">
       <c r="B59" s="2" t="s">
         <v>55</v>
       </c>
       <c r="AN59" s="2"/>
       <c r="CD59" s="2"/>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B65" s="2"/>
     </row>
-    <row r="82" spans="1:82" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:82" x14ac:dyDescent="0.45">
       <c r="B82" s="2"/>
     </row>
-    <row r="85" spans="1:82" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:82" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
         <v>0</v>
       </c>
@@ -8757,141 +8806,141 @@
         <v>51</v>
       </c>
     </row>
-    <row r="86" spans="1:82" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:82" x14ac:dyDescent="0.45">
       <c r="B86" s="2" t="s">
         <v>52</v>
       </c>
       <c r="AN86" s="2"/>
       <c r="CD86" s="2"/>
     </row>
-    <row r="92" spans="1:82" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:82" x14ac:dyDescent="0.45">
       <c r="B92" s="2"/>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B106" s="2"/>
     </row>
-    <row r="124" spans="1:82" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" s="1" t="s">
+    <row r="122" spans="1:82" x14ac:dyDescent="0.45">
+      <c r="A122" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B122" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="125" spans="1:82" x14ac:dyDescent="0.55000000000000004">
-      <c r="B125" s="2" t="s">
+    <row r="123" spans="1:82" x14ac:dyDescent="0.45">
+      <c r="B123" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AN125" s="2"/>
-      <c r="CD125" s="2"/>
-    </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B130" s="2"/>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B145" s="2"/>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A160" s="1" t="s">
+      <c r="AN123" s="2"/>
+      <c r="CD123" s="2"/>
+    </row>
+    <row r="128" spans="1:82" x14ac:dyDescent="0.45">
+      <c r="B128" s="2"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B143" s="2"/>
+    </row>
+    <row r="158" spans="1:82" x14ac:dyDescent="0.45">
+      <c r="A158" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B160" s="2" t="s">
+      <c r="B158" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="161" spans="2:82" x14ac:dyDescent="0.55000000000000004">
-      <c r="B161" s="2" t="s">
+    <row r="159" spans="1:82" x14ac:dyDescent="0.45">
+      <c r="B159" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AN161" s="2"/>
-      <c r="CD161" s="2"/>
-    </row>
-    <row r="164" spans="2:82" x14ac:dyDescent="0.55000000000000004">
-      <c r="B164" s="2"/>
-    </row>
-    <row r="168" spans="2:82" x14ac:dyDescent="0.55000000000000004">
-      <c r="B168" s="2"/>
-    </row>
-    <row r="183" spans="1:82" x14ac:dyDescent="0.55000000000000004">
-      <c r="B183" s="2"/>
-    </row>
-    <row r="187" spans="1:82" x14ac:dyDescent="0.55000000000000004">
-      <c r="A187" s="1" t="s">
+      <c r="AN159" s="2"/>
+      <c r="CD159" s="2"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B162" s="2"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B166" s="2"/>
+    </row>
+    <row r="181" spans="1:82" x14ac:dyDescent="0.45">
+      <c r="B181" s="2"/>
+    </row>
+    <row r="185" spans="1:82" x14ac:dyDescent="0.45">
+      <c r="A185" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B187" s="2" t="s">
+      <c r="B185" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="188" spans="1:82" x14ac:dyDescent="0.55000000000000004">
-      <c r="B188" s="2" t="s">
+    <row r="186" spans="1:82" x14ac:dyDescent="0.45">
+      <c r="B186" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AN188" s="2"/>
-      <c r="CD188" s="2"/>
-    </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B203" s="2"/>
-    </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B222" s="2"/>
-    </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B236" s="2"/>
-    </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B249" s="2"/>
-    </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B258" s="2"/>
-    </row>
-    <row r="277" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B277" s="2"/>
-    </row>
-    <row r="289" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B289" s="2"/>
-    </row>
-    <row r="301" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B301" s="2"/>
-    </row>
-    <row r="330" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B330" s="2"/>
-    </row>
-    <row r="333" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B333" s="3"/>
-    </row>
-    <row r="356" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B356" s="2"/>
-    </row>
-    <row r="365" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B365" s="2"/>
-    </row>
-    <row r="383" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B383" s="2"/>
-    </row>
-    <row r="384" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B384" s="2"/>
-    </row>
-    <row r="410" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B410" s="2"/>
-    </row>
-    <row r="419" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B419" s="2"/>
-    </row>
-    <row r="436" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B436" s="2"/>
-    </row>
-    <row r="469" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B469" s="2"/>
-    </row>
-    <row r="511" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B511" s="2"/>
-    </row>
-    <row r="538" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B538" s="2"/>
-    </row>
-    <row r="573" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B573" s="2"/>
+      <c r="AN186" s="2"/>
+      <c r="CD186" s="2"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B201" s="2"/>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B220" s="2"/>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B234" s="2"/>
+    </row>
+    <row r="247" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B247" s="2"/>
+    </row>
+    <row r="256" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B256" s="2"/>
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B275" s="2"/>
+    </row>
+    <row r="287" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B287" s="2"/>
+    </row>
+    <row r="299" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B299" s="2"/>
+    </row>
+    <row r="328" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B328" s="2"/>
+    </row>
+    <row r="331" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B331" s="3"/>
+    </row>
+    <row r="354" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B354" s="2"/>
+    </row>
+    <row r="363" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B363" s="2"/>
+    </row>
+    <row r="381" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B381" s="2"/>
+    </row>
+    <row r="382" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B382" s="2"/>
+    </row>
+    <row r="408" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B408" s="2"/>
+    </row>
+    <row r="417" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B417" s="2"/>
+    </row>
+    <row r="434" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B434" s="2"/>
+    </row>
+    <row r="467" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B467" s="2"/>
+    </row>
+    <row r="509" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B509" s="2"/>
+    </row>
+    <row r="536" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B536" s="2"/>
+    </row>
+    <row r="571" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B571" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -8903,12 +8952,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A29FA320-DA47-41A9-9EA7-7E68689E0E1F}">
   <dimension ref="A1:ED573"/>
-  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="3.08203125" style="1"/>
+    <col min="1" max="16384" width="3.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:134" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -9306,7 +9355,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:134" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -9326,7 +9375,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:134" x14ac:dyDescent="0.45">
       <c r="AN4" s="1" t="s">
         <v>40</v>
       </c>
@@ -9334,7 +9383,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:134" x14ac:dyDescent="0.45">
       <c r="AN5" s="1" t="s">
         <v>37</v>
       </c>
@@ -9342,7 +9391,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:134" x14ac:dyDescent="0.45">
       <c r="AN6" s="1" t="s">
         <v>41</v>
       </c>
@@ -9350,12 +9399,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:134" x14ac:dyDescent="0.45">
       <c r="CD7" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -9363,15 +9412,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B42" s="2"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
         <v>0</v>
       </c>
@@ -9379,20 +9428,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B66" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B67" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B82" s="2"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
         <v>0</v>
       </c>
@@ -9400,15 +9449,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B93" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B106" s="2"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
         <v>0</v>
       </c>
@@ -9416,18 +9465,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B131" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B145" s="2"/>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B164" s="2"/>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
         <v>0</v>
       </c>
@@ -9435,12 +9484,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B169" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
         <v>0</v>
       </c>
@@ -9448,20 +9497,20 @@
         <v>12</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B184" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B185" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B203" s="2"/>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A222" s="1" t="s">
         <v>0</v>
       </c>
@@ -9469,20 +9518,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B223" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B224" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B236" s="2"/>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A249" s="1" t="s">
         <v>0</v>
       </c>
@@ -9490,28 +9539,28 @@
         <v>18</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B250" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B251" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B252" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B258" s="2"/>
     </row>
-    <row r="277" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B277" s="2"/>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A289" s="1" t="s">
         <v>0</v>
       </c>
@@ -9519,20 +9568,20 @@
         <v>21</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B290" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B291" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B301" s="2"/>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A330" s="1" t="s">
         <v>0</v>
       </c>
@@ -9540,25 +9589,25 @@
         <v>25</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B331" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B332" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B333" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B356" s="2"/>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A365" s="1" t="s">
         <v>0</v>
       </c>
@@ -9566,15 +9615,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B366" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B383" s="2"/>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A384" s="1" t="s">
         <v>0</v>
       </c>
@@ -9582,20 +9631,20 @@
         <v>30</v>
       </c>
     </row>
-    <row r="385" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="385" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B385" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="386" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="386" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B386" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="410" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="410" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B410" s="2"/>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A419" s="1" t="s">
         <v>0</v>
       </c>
@@ -9603,29 +9652,29 @@
         <v>33</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B420" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B421" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="436" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="436" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B436" s="2"/>
     </row>
-    <row r="469" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="469" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B469" s="2"/>
     </row>
-    <row r="511" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="511" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B511" s="2"/>
     </row>
-    <row r="538" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="538" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B538" s="2"/>
     </row>
-    <row r="573" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="573" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B573" s="2"/>
     </row>
   </sheetData>
